--- a/src/test/resources/testdata/SweetBalanceApplication.xlsx
+++ b/src/test/resources/testdata/SweetBalanceApplication.xlsx
@@ -5,18 +5,139 @@
     <workbookView xWindow="0" yWindow="40" windowWidth="15960" windowHeight="18080"/>
   </bookViews>
   <sheets>
-    <sheet name="sheet1" sheetId="1" r:id="rId4"/>
+    <sheet name="Export Summary" sheetId="1" r:id="rId4"/>
+    <sheet name="sheet1" sheetId="2" r:id="rId5"/>
+    <sheet name="Sheet2" sheetId="3" r:id="rId6"/>
+    <sheet name="Sheet 1" sheetId="4" r:id="rId7"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="30">
+  <si>
+    <t>This document was exported from Numbers.  Each table was converted to an Excel worksheet. All other objects on each Numbers sheet were placed on separate worksheets. Please be aware that formula calculations may differ in Excel.</t>
+  </si>
+  <si>
+    <t>Numbers Sheet Name</t>
+  </si>
+  <si>
+    <t>Numbers Table Name</t>
+  </si>
+  <si>
+    <t>Excel Worksheet Name</t>
+  </si>
+  <si>
+    <t>Export Summary</t>
+  </si>
+  <si>
+    <t>Table 1</t>
+  </si>
+  <si>
+    <t>sheet1</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u val="single"/>
+        <sz val="12"/>
+        <color indexed="11"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>sheet1</t>
+    </r>
+  </si>
+  <si>
+    <t>Sheet2</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u val="single"/>
+        <sz val="12"/>
+        <color indexed="11"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>Sheet2</t>
+    </r>
+  </si>
+  <si>
+    <t>Sheet 1</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u val="single"/>
+        <sz val="12"/>
+        <color indexed="11"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>Sheet 1</t>
+    </r>
+  </si>
   <si>
     <t>Email</t>
   </si>
   <si>
     <t>Password</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u val="single"/>
+        <sz val="11"/>
+        <color indexed="14"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>dnd.dinesh22@gmail.com</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u val="single"/>
+        <sz val="11"/>
+        <color indexed="14"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>ninja@12345</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u val="single"/>
+        <sz val="11"/>
+        <color indexed="14"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>pramodini.patil182@gmail.com</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u val="single"/>
+        <sz val="11"/>
+        <color indexed="14"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>pramodini@182</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u val="single"/>
+        <sz val="11"/>
+        <color indexed="14"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>treaty123@gmail.com</t>
+    </r>
+  </si>
+  <si>
+    <t>Donaldduck</t>
   </si>
   <si>
     <r>
@@ -26,66 +147,51 @@
         <color indexed="11"/>
         <rFont val="Aptos Narrow"/>
       </rPr>
-      <t>dnd.dinesh22@gmail.com</t>
+      <t>eureka@gmail.com</t>
     </r>
+  </si>
+  <si>
+    <t>fullName</t>
+  </si>
+  <si>
+    <t>username</t>
+  </si>
+  <si>
+    <t>password</t>
+  </si>
+  <si>
+    <t>Hyderali</t>
   </si>
   <si>
     <r>
       <rPr>
         <u val="single"/>
-        <sz val="11"/>
+        <sz val="12"/>
         <color indexed="11"/>
         <rFont val="Aptos Narrow"/>
       </rPr>
-      <t>ninja@12345</t>
+      <t>newuser1@test.com</t>
     </r>
+  </si>
+  <si>
+    <t>Pass123!</t>
+  </si>
+  <si>
+    <t>Relelalali</t>
   </si>
   <si>
     <r>
       <rPr>
         <u val="single"/>
-        <sz val="11"/>
+        <sz val="12"/>
         <color indexed="11"/>
         <rFont val="Aptos Narrow"/>
       </rPr>
-      <t>pramodini.patil182@gmail.com</t>
+      <t>newuser2@test.com</t>
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <sz val="11"/>
-        <color indexed="11"/>
-        <rFont val="Aptos Narrow"/>
-      </rPr>
-      <t>pramodini@182</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <sz val="11"/>
-        <color indexed="11"/>
-        <rFont val="Aptos Narrow"/>
-      </rPr>
-      <t>treaty123@gmail.com</t>
-    </r>
-  </si>
-  <si>
-    <t>Donaldduck</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <sz val="11"/>
-        <color indexed="12"/>
-        <rFont val="Aptos Narrow"/>
-      </rPr>
-      <t>eureka@gmail.com</t>
-    </r>
+    <t>Secret@456</t>
   </si>
 </sst>
 </file>
@@ -95,9 +201,19 @@
   <numFmts count="1">
     <numFmt numFmtId="0" formatCode="General"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="11">
     <font>
       <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color indexed="8"/>
+      <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <sz val="14"/>
       <color indexed="8"/>
       <name val="Aptos Narrow"/>
     </font>
@@ -107,9 +223,21 @@
       <name val="Helvetica Neue"/>
     </font>
     <font>
+      <u val="single"/>
+      <sz val="12"/>
+      <color indexed="11"/>
+      <name val="Aptos Narrow"/>
+    </font>
+    <font>
       <sz val="15"/>
       <color indexed="8"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <u val="single"/>
+      <sz val="11"/>
+      <color indexed="14"/>
+      <name val="Aptos Narrow"/>
     </font>
     <font>
       <u val="single"/>
@@ -118,13 +246,24 @@
       <name val="Aptos Narrow"/>
     </font>
     <font>
-      <u val="single"/>
+      <sz val="15"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
+      <color indexed="8"/>
+      <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <b val="1"/>
       <sz val="11"/>
-      <color indexed="12"/>
+      <color indexed="8"/>
       <name val="Aptos Narrow"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -137,8 +276,32 @@
         <bgColor auto="1"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="10"/>
+        <bgColor auto="1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="12"/>
+        <bgColor auto="1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="17"/>
+        <bgColor auto="1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="18"/>
+        <bgColor auto="1"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="25">
     <border>
       <left/>
       <right/>
@@ -148,16 +311,297 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="10"/>
+        <color indexed="13"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="13"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="13"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="13"/>
+      </right>
+      <top style="thin">
+        <color indexed="13"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="13"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="13"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="13"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="13"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="13"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="13"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="13"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="13"/>
       </left>
       <right style="thin">
-        <color indexed="10"/>
+        <color indexed="13"/>
       </right>
       <top style="thin">
-        <color indexed="10"/>
+        <color indexed="13"/>
       </top>
       <bottom style="thin">
-        <color indexed="10"/>
+        <color indexed="13"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="13"/>
+      </left>
+      <right style="thin">
+        <color indexed="13"/>
+      </right>
+      <top style="thin">
+        <color indexed="13"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="15"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="13"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="13"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="15"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="13"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="15"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="13"/>
+      </right>
+      <top style="thin">
+        <color indexed="13"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="15"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="16"/>
+      </left>
+      <right style="thin">
+        <color indexed="16"/>
+      </right>
+      <top style="thin">
+        <color indexed="15"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="16"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="16"/>
+      </left>
+      <right style="thin">
+        <color indexed="15"/>
+      </right>
+      <top style="thin">
+        <color indexed="15"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="16"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="15"/>
+      </left>
+      <right style="thin">
+        <color indexed="16"/>
+      </right>
+      <top style="thin">
+        <color indexed="15"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="16"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="16"/>
+      </left>
+      <right style="thin">
+        <color indexed="16"/>
+      </right>
+      <top style="thin">
+        <color indexed="16"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="16"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="16"/>
+      </left>
+      <right style="thin">
+        <color indexed="15"/>
+      </right>
+      <top style="thin">
+        <color indexed="16"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="16"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="15"/>
+      </left>
+      <right style="thin">
+        <color indexed="16"/>
+      </right>
+      <top style="thin">
+        <color indexed="16"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="16"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="13"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="13"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="16"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="13"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="16"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="13"/>
+      </right>
+      <top style="thin">
+        <color indexed="13"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="16"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="16"/>
+      </left>
+      <right style="thin">
+        <color indexed="16"/>
+      </right>
+      <top style="thin">
+        <color indexed="16"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="15"/>
       </bottom>
       <diagonal/>
     </border>
@@ -167,21 +611,162 @@
       <alignment vertical="bottom"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
+    <xf numFmtId="0" fontId="1" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
     <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="4" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="4" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="11" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="12" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="13" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="14" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="4" borderId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="4" borderId="16" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="4" borderId="17" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="4" borderId="18" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="4" borderId="19" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="4" borderId="20" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="18" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="18" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="19" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="20" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="4" borderId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="22" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="23" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="24" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="16" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="17" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -200,10 +785,16 @@
       <rgbColor rgb="ffff00ff"/>
       <rgbColor rgb="ff00ffff"/>
       <rgbColor rgb="ff000000"/>
+      <rgbColor rgb="ff5e88b1"/>
+      <rgbColor rgb="ffeef3f4"/>
+      <rgbColor rgb="ff0000ff"/>
       <rgbColor rgb="ffffffff"/>
       <rgbColor rgb="ffaaaaaa"/>
       <rgbColor rgb="ff467886"/>
-      <rgbColor rgb="ff0000ff"/>
+      <rgbColor rgb="ff3f3f3f"/>
+      <rgbColor rgb="ffa5a5a5"/>
+      <rgbColor rgb="ffdbdbdb"/>
+      <rgbColor rgb="ffbdc0bf"/>
     </indexedColors>
   </colors>
 </styleSheet>
@@ -1265,106 +1856,291 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr defaultColWidth="10" defaultRowHeight="13" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col min="1" max="1" width="2" customWidth="1"/>
+    <col min="1" max="1" width="2" style="6" customWidth="1"/>
+    <col min="2" max="4" width="30.5547" customWidth="1"/>
+    <col min="2" max="2" width="30.5" style="6" customWidth="1"/>
+    <col min="3" max="3" width="30.5" style="6" customWidth="1"/>
+    <col min="4" max="4" width="30.5" style="6" customWidth="1"/>
+    <col min="5" max="5" width="10" style="6" customWidth="1"/>
+    <col min="6" max="16384" width="10" style="6" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="16" customHeight="1">
+      <c r="A1" s="7"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="9"/>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="10"/>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="12"/>
+    </row>
+    <row r="3" ht="50" customHeight="1">
+      <c r="A3" s="10"/>
+      <c r="B3" t="s" s="13">
+        <v>0</v>
+      </c>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="12"/>
+    </row>
+    <row r="4" ht="16" customHeight="1">
+      <c r="A4" s="10"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="12"/>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="10"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="11"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="12"/>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" s="10"/>
+      <c r="B6" s="11"/>
+      <c r="C6" s="11"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="12"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="10"/>
+      <c r="B7" t="s" s="14">
+        <v>1</v>
+      </c>
+      <c r="C7" t="s" s="14">
+        <v>2</v>
+      </c>
+      <c r="D7" t="s" s="14">
+        <v>3</v>
+      </c>
+      <c r="E7" s="12"/>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="10"/>
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="12"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="10"/>
+      <c r="B9" t="s" s="15">
+        <v>6</v>
+      </c>
+      <c r="C9" s="16"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="12"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="10"/>
+      <c r="B10" s="17"/>
+      <c r="C10" t="s" s="18">
+        <v>5</v>
+      </c>
+      <c r="D10" t="s" s="19">
+        <v>7</v>
+      </c>
+      <c r="E10" s="12"/>
+    </row>
+    <row r="11" ht="13" customHeight="1">
+      <c r="A11" s="10"/>
+      <c r="B11" t="s" s="3">
+        <v>6</v>
+      </c>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="12"/>
+    </row>
+    <row r="12" ht="13" customHeight="1">
+      <c r="A12" s="20"/>
+      <c r="B12" s="4"/>
+      <c r="C12" t="s" s="4">
+        <v>5</v>
+      </c>
+      <c r="D12" t="s" s="5">
+        <v>6</v>
+      </c>
+      <c r="E12" s="21"/>
+    </row>
+    <row r="13" ht="13" customHeight="1">
+      <c r="A13" s="7"/>
+      <c r="B13" t="s" s="3">
+        <v>8</v>
+      </c>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="9"/>
+    </row>
+    <row r="14" ht="13" customHeight="1">
+      <c r="A14" s="10"/>
+      <c r="B14" s="4"/>
+      <c r="C14" t="s" s="4">
+        <v>5</v>
+      </c>
+      <c r="D14" t="s" s="5">
+        <v>8</v>
+      </c>
+      <c r="E14" s="12"/>
+    </row>
+    <row r="15" ht="13" customHeight="1">
+      <c r="A15" s="10"/>
+      <c r="B15" t="s" s="3">
+        <v>10</v>
+      </c>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="12"/>
+    </row>
+    <row r="16" ht="13" customHeight="1">
+      <c r="A16" s="20"/>
+      <c r="B16" s="4"/>
+      <c r="C16" t="s" s="4">
+        <v>5</v>
+      </c>
+      <c r="D16" t="s" s="5">
+        <v>10</v>
+      </c>
+      <c r="E16" s="21"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="B3:D3"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="D10" location="'Export Summary'!R1C1" tooltip="" display="Export Summary"/>
+    <hyperlink ref="D10" location="'sheet1'!R1C1" tooltip="" display="sheet1"/>
+    <hyperlink ref="D12" location="'sheet1'!R1C1" tooltip="" display="sheet1"/>
+    <hyperlink ref="D14" location="'Sheet2'!R1C1" tooltip="" display="Sheet2"/>
+    <hyperlink ref="D16" location="'Sheet 1'!R1C1" tooltip="" display="Sheet 1"/>
+    <hyperlink ref="D12" location="'sheet1'!R1C1" tooltip="" display="sheet1"/>
+    <hyperlink ref="D14" location="'Sheet2'!R1C1" tooltip="" display="Sheet2"/>
+    <hyperlink ref="D16" location="'Sheet 1'!R1C1" tooltip="" display="Sheet 1"/>
+  </hyperlinks>
+  <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
+  <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
+  <headerFooter>
+    <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:E10"/>
   <sheetFormatPr defaultColWidth="8.83333" defaultRowHeight="15" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="32.1797" style="1" customWidth="1"/>
-    <col min="2" max="2" width="39.4297" style="1" customWidth="1"/>
-    <col min="3" max="5" width="8.85156" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="8.85156" style="1" customWidth="1"/>
+    <col min="1" max="1" width="32.1719" style="25" customWidth="1"/>
+    <col min="2" max="2" width="39.5" style="25" customWidth="1"/>
+    <col min="3" max="5" width="8.85156" style="25" customWidth="1"/>
+    <col min="6" max="16384" width="8.85156" style="25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="16" customHeight="1">
-      <c r="A1" t="s" s="2">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s" s="2">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
+      <c r="A1" t="s" s="26">
+        <v>12</v>
+      </c>
+      <c r="B1" t="s" s="26">
+        <v>13</v>
+      </c>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
     </row>
     <row r="2" ht="48" customHeight="1">
-      <c r="A2" t="s" s="2">
-        <v>2</v>
-      </c>
-      <c r="B2" t="s" s="2">
-        <v>3</v>
-      </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
+      <c r="A2" t="s" s="26">
+        <v>14</v>
+      </c>
+      <c r="B2" t="s" s="26">
+        <v>15</v>
+      </c>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
     </row>
     <row r="3" ht="64" customHeight="1">
-      <c r="A3" t="s" s="2">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>5</v>
-      </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
+      <c r="A3" t="s" s="26">
+        <v>16</v>
+      </c>
+      <c r="B3" t="s" s="26">
+        <v>17</v>
+      </c>
+      <c r="C3" s="27"/>
+      <c r="D3" s="27"/>
+      <c r="E3" s="27"/>
     </row>
     <row r="4" ht="42" customHeight="1">
-      <c r="A4" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
+      <c r="A4" t="s" s="26">
+        <v>18</v>
+      </c>
+      <c r="B4" t="s" s="26">
+        <v>19</v>
+      </c>
+      <c r="C4" s="27"/>
+      <c r="D4" s="27"/>
+      <c r="E4" s="27"/>
     </row>
     <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="4">
+      <c r="A5" s="28">
         <v>123456</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5" s="28">
         <v>123456</v>
       </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
+      <c r="C5" s="27"/>
+      <c r="D5" s="27"/>
+      <c r="E5" s="27"/>
     </row>
     <row r="6" ht="16" customHeight="1">
-      <c r="A6" t="s" s="2">
-        <v>8</v>
-      </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
+      <c r="A6" t="s" s="26">
+        <v>20</v>
+      </c>
+      <c r="B6" s="27"/>
+      <c r="C6" s="27"/>
+      <c r="D6" s="27"/>
+      <c r="E6" s="27"/>
     </row>
     <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
+      <c r="A7" s="27"/>
+      <c r="B7" s="27"/>
+      <c r="C7" s="27"/>
+      <c r="D7" s="27"/>
+      <c r="E7" s="27"/>
     </row>
     <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
+      <c r="A8" s="27"/>
+      <c r="B8" s="27"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
     </row>
     <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
+      <c r="A9" s="27"/>
+      <c r="B9" s="27"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="27"/>
     </row>
     <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
+      <c r="A10" s="27"/>
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -1381,4 +2157,234 @@
     <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr defaultColWidth="16.3333" defaultRowHeight="13" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col min="1" max="2" width="26.8516" style="29" customWidth="1"/>
+    <col min="3" max="6" width="16.3516" style="29" customWidth="1"/>
+    <col min="7" max="16384" width="16.3516" style="29" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15.55" customHeight="1">
+      <c r="A1" s="30"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="33"/>
+    </row>
+    <row r="2" ht="16.55" customHeight="1">
+      <c r="A2" t="s" s="34">
+        <v>21</v>
+      </c>
+      <c r="B2" t="s" s="35">
+        <v>22</v>
+      </c>
+      <c r="C2" t="s" s="36">
+        <v>23</v>
+      </c>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+    </row>
+    <row r="3" ht="16.35" customHeight="1">
+      <c r="A3" t="s" s="38">
+        <v>24</v>
+      </c>
+      <c r="B3" t="s" s="39">
+        <v>25</v>
+      </c>
+      <c r="C3" t="s" s="40">
+        <v>26</v>
+      </c>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
+    </row>
+    <row r="4" ht="16.35" customHeight="1">
+      <c r="A4" t="s" s="38">
+        <v>27</v>
+      </c>
+      <c r="B4" t="s" s="39">
+        <v>28</v>
+      </c>
+      <c r="C4" t="s" s="40">
+        <v>29</v>
+      </c>
+      <c r="D4" s="41"/>
+      <c r="E4" s="41"/>
+      <c r="F4" s="41"/>
+    </row>
+    <row r="5" ht="15.35" customHeight="1">
+      <c r="A5" s="42"/>
+      <c r="B5" s="43"/>
+      <c r="C5" s="44"/>
+      <c r="D5" s="41"/>
+      <c r="E5" s="41"/>
+      <c r="F5" s="41"/>
+    </row>
+    <row r="6" ht="15.35" customHeight="1">
+      <c r="A6" s="42"/>
+      <c r="B6" s="43"/>
+      <c r="C6" s="44"/>
+      <c r="D6" s="41"/>
+      <c r="E6" s="41"/>
+      <c r="F6" s="41"/>
+    </row>
+    <row r="7" ht="15.35" customHeight="1">
+      <c r="A7" s="42"/>
+      <c r="B7" s="43"/>
+      <c r="C7" s="44"/>
+      <c r="D7" s="41"/>
+      <c r="E7" s="41"/>
+      <c r="F7" s="41"/>
+    </row>
+    <row r="8" ht="15.35" customHeight="1">
+      <c r="A8" s="42"/>
+      <c r="B8" s="43"/>
+      <c r="C8" s="44"/>
+      <c r="D8" s="41"/>
+      <c r="E8" s="41"/>
+      <c r="F8" s="41"/>
+    </row>
+    <row r="9" ht="15.35" customHeight="1">
+      <c r="A9" s="42"/>
+      <c r="B9" s="43"/>
+      <c r="C9" s="44"/>
+      <c r="D9" s="41"/>
+      <c r="E9" s="41"/>
+      <c r="F9" s="41"/>
+    </row>
+    <row r="10" ht="15.35" customHeight="1">
+      <c r="A10" s="42"/>
+      <c r="B10" s="43"/>
+      <c r="C10" s="44"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="41"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B1:F1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="B3" r:id="rId1" location="" tooltip="" display="newuser1@test.com"/>
+    <hyperlink ref="B4" r:id="rId2" location="" tooltip="" display="newuser2@test.com"/>
+  </hyperlinks>
+  <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
+  <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
+  <headerFooter>
+    <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr defaultColWidth="16.3333" defaultRowHeight="13" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col min="1" max="5" width="16.3516" style="45" customWidth="1"/>
+    <col min="6" max="16384" width="16.3516" style="45" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15.55" customHeight="1">
+      <c r="A1" t="s" s="46">
+        <v>5</v>
+      </c>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="48"/>
+    </row>
+    <row r="2" ht="15.55" customHeight="1">
+      <c r="A2" s="49"/>
+      <c r="B2" s="49"/>
+      <c r="C2" s="49"/>
+      <c r="D2" s="49"/>
+      <c r="E2" s="49"/>
+    </row>
+    <row r="3" ht="15.55" customHeight="1">
+      <c r="A3" s="50"/>
+      <c r="B3" s="51"/>
+      <c r="C3" s="37"/>
+      <c r="D3" s="37"/>
+      <c r="E3" s="37"/>
+    </row>
+    <row r="4" ht="15.35" customHeight="1">
+      <c r="A4" s="43"/>
+      <c r="B4" s="44"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="41"/>
+    </row>
+    <row r="5" ht="15.35" customHeight="1">
+      <c r="A5" s="43"/>
+      <c r="B5" s="44"/>
+      <c r="C5" s="41"/>
+      <c r="D5" s="41"/>
+      <c r="E5" s="41"/>
+    </row>
+    <row r="6" ht="15.35" customHeight="1">
+      <c r="A6" s="43"/>
+      <c r="B6" s="44"/>
+      <c r="C6" s="41"/>
+      <c r="D6" s="41"/>
+      <c r="E6" s="41"/>
+    </row>
+    <row r="7" ht="15.35" customHeight="1">
+      <c r="A7" s="43"/>
+      <c r="B7" s="44"/>
+      <c r="C7" s="41"/>
+      <c r="D7" s="41"/>
+      <c r="E7" s="41"/>
+    </row>
+    <row r="8" ht="15.35" customHeight="1">
+      <c r="A8" s="43"/>
+      <c r="B8" s="44"/>
+      <c r="C8" s="41"/>
+      <c r="D8" s="41"/>
+      <c r="E8" s="41"/>
+    </row>
+    <row r="9" ht="15.35" customHeight="1">
+      <c r="A9" s="43"/>
+      <c r="B9" s="44"/>
+      <c r="C9" s="41"/>
+      <c r="D9" s="41"/>
+      <c r="E9" s="41"/>
+    </row>
+    <row r="10" ht="15.35" customHeight="1">
+      <c r="A10" s="43"/>
+      <c r="B10" s="44"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="41"/>
+    </row>
+    <row r="11" ht="15.35" customHeight="1">
+      <c r="A11" s="43"/>
+      <c r="B11" s="44"/>
+      <c r="C11" s="41"/>
+      <c r="D11" s="41"/>
+      <c r="E11" s="41"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
+  <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
+  <headerFooter>
+    <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
 </file>